--- a/storage/app/SFOC Konstan.xlsx
+++ b/storage/app/SFOC Konstan.xlsx
@@ -415,7 +415,7 @@
         <v>ASR</v>
       </c>
       <c r="B2" t="str">
-        <v>1.2</v>
+        <v>178.8</v>
       </c>
       <c r="C2" t="str">
         <v>g/kW/hr</v>
@@ -426,7 +426,7 @@
         <v>ASN</v>
       </c>
       <c r="B3" t="str">
-        <v>1.2</v>
+        <v>178.8</v>
       </c>
       <c r="C3" t="str">
         <v>g/kW/hr</v>
@@ -437,7 +437,7 @@
         <v>ASG</v>
       </c>
       <c r="B4" t="str">
-        <v>1.2</v>
+        <v>178.8</v>
       </c>
       <c r="C4" t="str">
         <v>g/kW/hr</v>

--- a/storage/app/SFOC Konstan.xlsx
+++ b/storage/app/SFOC Konstan.xlsx
@@ -415,7 +415,7 @@
         <v>ASR</v>
       </c>
       <c r="B2" t="str">
-        <v>178.8</v>
+        <v>112</v>
       </c>
       <c r="C2" t="str">
         <v>g/kW/hr</v>
@@ -426,7 +426,7 @@
         <v>ASN</v>
       </c>
       <c r="B3" t="str">
-        <v>178.8</v>
+        <v>112</v>
       </c>
       <c r="C3" t="str">
         <v>g/kW/hr</v>
@@ -437,7 +437,7 @@
         <v>ASG</v>
       </c>
       <c r="B4" t="str">
-        <v>178.8</v>
+        <v>112</v>
       </c>
       <c r="C4" t="str">
         <v>g/kW/hr</v>

--- a/storage/app/SFOC Konstan.xlsx
+++ b/storage/app/SFOC Konstan.xlsx
@@ -415,7 +415,7 @@
         <v>ASR</v>
       </c>
       <c r="B2" t="str">
-        <v>112</v>
+        <v>60</v>
       </c>
       <c r="C2" t="str">
         <v>g/kW/hr</v>
@@ -426,7 +426,7 @@
         <v>ASN</v>
       </c>
       <c r="B3" t="str">
-        <v>112</v>
+        <v>60</v>
       </c>
       <c r="C3" t="str">
         <v>g/kW/hr</v>
@@ -437,7 +437,7 @@
         <v>ASG</v>
       </c>
       <c r="B4" t="str">
-        <v>112</v>
+        <v>60</v>
       </c>
       <c r="C4" t="str">
         <v>g/kW/hr</v>

--- a/storage/app/SFOC Konstan.xlsx
+++ b/storage/app/SFOC Konstan.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C5"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -412,84 +412,51 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>ASR</v>
+        <v>APE</v>
       </c>
       <c r="B2" t="str">
-        <v>60</v>
+        <v>121.4</v>
       </c>
       <c r="C2" t="str">
-        <v>g/kW/hr</v>
+        <v>g/BHP/hr_x000d_</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>ASN</v>
+        <v>PFA</v>
       </c>
       <c r="B3" t="str">
-        <v>60</v>
+        <v>200.8</v>
       </c>
       <c r="C3" t="str">
-        <v>g/kW/hr</v>
+        <v>g/kW/hr_x000d_</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>ASG</v>
+        <v>PRI</v>
       </c>
       <c r="B4" t="str">
-        <v>60</v>
+        <v>200.8</v>
       </c>
       <c r="C4" t="str">
-        <v>g/kW/hr</v>
+        <v>g/kW/hr_x000d_</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>APE</v>
+        <v>ODI</v>
       </c>
       <c r="B5" t="str">
-        <v>121.4</v>
+        <v>126</v>
       </c>
       <c r="C5" t="str">
-        <v>g/BHP/hr</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>PFA</v>
-      </c>
-      <c r="B6" t="str">
-        <v>200.8</v>
-      </c>
-      <c r="C6" t="str">
-        <v>g/kW/hr</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>PRI</v>
-      </c>
-      <c r="B7" t="str">
-        <v>200.8</v>
-      </c>
-      <c r="C7" t="str">
-        <v>g/kW/hr</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>ODI</v>
-      </c>
-      <c r="B8" t="str">
-        <v>126</v>
-      </c>
-      <c r="C8" t="str">
         <v>g/BHP/hr</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C8"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C5"/>
   </ignoredErrors>
 </worksheet>
 </file>